--- a/data/trending_integrated_20260917_13.xlsx
+++ b/data/trending_integrated_20260917_13.xlsx
@@ -584,7 +584,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 횡보 구간에서 개인 매수세 유입 및 300원 돌파 기대감. BPS 대비 저평가 가능성.</t>
+          <t>회사의 재무 상태 및 경영진에 대한 의문이 제기되지만, 특정 가격대 돌파 및 상승 가능성에 대한 기대도 일부 존재함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상승', '개미', 'BPS']</t>
+          <t>['재무상태', '주가상승', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.69%</t>
+          <t>'+23.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
         <v>3.52</v>
@@ -702,7 +702,7 @@
         <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>46814946306</v>
+        <v>47954449594</v>
       </c>
       <c r="P3" t="n">
         <v>5140</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4585</v>
+        <v>4570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.40%</t>
+          <t>'+19.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G4" t="n">
-        <v>1199</v>
+        <v>1228</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>235442973386</v>
+        <v>237360199886</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22050</v>
+        <v>21850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+18.80%</t>
+          <t>'+17.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>273738927920</v>
+        <v>277616955745</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3925</v>
+        <v>3885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.14%</t>
+          <t>'+11.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>89473165490</v>
+        <v>91761806926</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 사업 진출 기대감과 함께, 단기 급등에 대한 긍정적 전망. 프로그램 매수세 관찰.</t>
+          <t>스페이스X 관련 사업 기대감과 함께 급등 가능성이 언급되며, 주포의 매집 정황 및 긍정적인 추세 분석이 제시됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '급등', '프로그램매수']</t>
+          <t>['스페이스X', '매집봉', '주포']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21750</v>
+        <v>21700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.67%</t>
+          <t>'+7.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>68601239475</v>
+        <v>69925205275</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1082,7 +1082,7 @@
         <v>902000</v>
       </c>
       <c r="S7" t="n">
-        <v>67000</v>
+        <v>191000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1130,13 +1130,13 @@
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>172865811245</v>
+        <v>173570070990</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 관련 기대감에도 불구하고, 주가 상승 요인에 대한 의구심 존재. 예상 매출 1조원 이상 언급.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감에도 불구하고, 주가 상승 동력이 외국인 및 기관 매도세로 인한 이탈 우려가 존재함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모 치료', '매출']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13460</v>
+        <v>13440</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>51967788295</v>
+        <v>52370785065</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86300</v>
+        <v>86500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F10" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>94552960800</v>
+        <v>97986812250</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1358,20 +1358,20 @@
         <v>-71000</v>
       </c>
       <c r="S10" t="n">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FOMC 금리 인상 악재 소멸 후 반등을 기대하며, 대미 원전 투자와 AI 관련 전력 수요 증가를 긍정적 요인으로 분석.</t>
+          <t>원전 관련 사업 기대감 및 금리 인상 후 전망에 대한 긍정적인 언급이 있으나, 공매도 및 협상 불확실성 우려도 존재함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금리 인상', '원전', 'AI']</t>
+          <t>['원전사업', '금리인상', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16250</v>
+        <v>18680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>1278</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K11" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L11" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M11" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>330410819040</v>
+        <v>46765142140</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-508000</v>
+        <v>-175000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 국내 광통신주 동반 상승 기대. 2만 원 목표 및 통신 장비 부족 호재 언급.</t>
+          <t>6천억원 규모 수주 발표에도 불구하고 주가 하락 및 금리 인상 우려. 대차해지 운동 동참 요청.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '통신 장비', '매물대 소화']</t>
+          <t>['수주', '금리인상', '대차해지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18690</v>
+        <v>254750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>456</v>
       </c>
       <c r="G12" t="n">
-        <v>338</v>
+        <v>1695</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M12" t="n">
-        <v>18510</v>
+        <v>252000</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>45792008570</v>
+        <v>1585568712000</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-175000</v>
+        <v>-199000</v>
       </c>
       <c r="S12" t="n">
-        <v>-31000</v>
+        <v>-231000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6천억원 규모 수주 발표에도 불구하고 주가 하락 및 금리 인상 우려. 대차해지 운동 동참 요청.</t>
+          <t>정치적 언급이 다수 포함되어 있으며, 주가 관련 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '금리인상', '대차해지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254750</v>
+        <v>16130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>244</v>
       </c>
       <c r="F13" t="n">
-        <v>450</v>
+        <v>136</v>
       </c>
       <c r="G13" t="n">
-        <v>1757</v>
+        <v>1287</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>16100</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>16200</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>16750</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>15560</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1533827738250</v>
+        <v>332899680850</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-199000</v>
+        <v>-508000</v>
       </c>
       <c r="S13" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 성향 논쟁이 주식 게시판에 나타나며, 특정 정치인에 대한 지지 및 비판이 혼재. 연기금의 매도세 관찰.</t>
+          <t>미국 광통신 시장 호황 및 국내 통신 장비 부족 현상에 따른 수혜 기대감이 높으며, 매물대 소화 후 추가 상승 가능성이 분석됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '연기금', '매도']</t>
+          <t>['광통신', '수혜주', '매물대소화']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1757000</v>
+        <v>1759000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G14" t="n">
-        <v>1575</v>
+        <v>1552</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2734693465500</v>
+        <v>2857786595000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1726,11 +1726,11 @@
         <v>-161000</v>
       </c>
       <c r="S14" t="n">
-        <v>-55000</v>
+        <v>-62000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>향후 상승 가능성에 대한 기대감과 함께, 단기 차익 실현 매매 선호 현상 관찰. 정치적 발언 혼재.</t>
+          <t>정치적 언급과 함께 단기적 반등 및 하락에 대한 기대가 혼재하며, 구체적인 팩트 기반 분석은 미흡함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['홀딩', '차익 실현', '반도체']</t>
+          <t>['자사주매입', '정치적악재']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1780,7 +1780,7 @@
         <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>10612738675</v>
+        <v>10896120035</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1818,20 +1818,20 @@
         <v>-263000</v>
       </c>
       <c r="S15" t="n">
-        <v>4000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>회사의 경영 능력 및 재무 상태에 대한 부정적 평가가 지배적. 빚 규모 및 영업이익 전망에 대한 불신.</t>
+          <t>부정적인 전망과 함께 회사의 재무 건전성 및 경영 능력에 대한 비판이 제기되며, 주가 하락 가능성이 언급됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['경영', '재무', '악재']</t>
+          <t>['재무건전성', '경영능력', '주가하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3465</v>
+        <v>13750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G16" t="n">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K16" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M16" t="n">
-        <v>3420</v>
+        <v>13410</v>
       </c>
       <c r="N16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5346344296</v>
+        <v>14385820995</v>
       </c>
       <c r="P16" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-279000</v>
+        <v>132000</v>
       </c>
       <c r="S16" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
+          <t>유가 관련 변동성 언급, 외국인 대량 매수 및 매도 패턴 관찰. VI 예상 및 400~300원 띠기 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '사기 주식']</t>
+          <t>['유가', 'VI']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13710</v>
+        <v>3460</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>13410</v>
+        <v>3420</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>14199606895</v>
+        <v>5388929516</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>132000</v>
+        <v>-279000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 관련 변동성 언급, 외국인 대량 매수 및 매도 패턴 관찰. VI 예상 및 400~300원 띠기 가능성.</t>
+          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', 'VI']</t>
+          <t>['상장폐지', '폭락', '사기 주식']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10240</v>
+        <v>10270</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>116</v>
@@ -2082,7 +2082,7 @@
         <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>55806384320</v>
+        <v>56082157465</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2094,7 +2094,7 @@
         <v>-60000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>-5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13210</v>
+        <v>13190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>80947353460</v>
+        <v>81167332450</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4190</v>
+        <v>4145</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>47559094344</v>
+        <v>48250819486</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_13.xlsx
+++ b/data/trending_integrated_20260917_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -619,23 +619,23 @@
         <v>56</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>회사의 재무 상태 및 경영진에 대한 의문이 제기되지만, 특정 가격대 돌파 및 상승 가능성에 대한 기대도 일부 존재함.</t>
+          <t>코다코 부채 언급하며 비교. 개미 물량 이탈 시 100원대 회복 가능성 언급. 300원 이상 상승 기대 및 제2 대한광통신 가능성 제기. 지분 매수 공시 부재 및 거래량 부진.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['재무상태', '주가상승', '거래량']</t>
+          <t>['거래량', '개미', '공시']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.05%</t>
+          <t>'+22.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H3" t="n">
         <v>3.52</v>
@@ -702,7 +702,7 @@
         <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>47954449594</v>
+        <v>49816980709</v>
       </c>
       <c r="P3" t="n">
         <v>5140</v>
@@ -711,7 +711,7 @@
         <v>870</v>
       </c>
       <c r="R3" t="n">
-        <v>72000</v>
+        <v>-32000</v>
       </c>
       <c r="S3" t="n">
         <v>-7000</v>
@@ -765,10 +765,10 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G4" t="n">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>237360199886</v>
+        <v>239247765036</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -803,7 +803,7 @@
         <v>1738</v>
       </c>
       <c r="R4" t="n">
-        <v>-159000</v>
+        <v>-150000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -854,13 +854,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>277616955745</v>
+        <v>279533239145</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -895,14 +895,14 @@
         <v>1030</v>
       </c>
       <c r="R5" t="n">
-        <v>-78000</v>
+        <v>-104000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 ADS테크의 CPO 장비 수주 및 AI 인프라 사업 확장을 통한 실적 개선 기대. 광통신주로서의 강세 부각.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CPO', 'AI 인프라', '광통신']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3885</v>
+        <v>3870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.00%</t>
+          <t>'+10.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>91761806926</v>
+        <v>92493766784</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -987,23 +987,23 @@
         <v>1913</v>
       </c>
       <c r="R6" t="n">
-        <v>-519000</v>
+        <v>-375000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 사업 기대감과 함께 급등 가능성이 언급되며, 주포의 매집 정황 및 긍정적인 추세 분석이 제시됨.</t>
+          <t>거래량 증가와 함께 11%대 상승 시도. 프로그램 매수세 유입 확인. 스페이스X 관련주로 부각되며 5천원 돌파 기대감 언급. 일부 매물대 소화 및 매집봉 형태 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '매집봉', '주포']</t>
+          <t>['스페이스X', '프로그램매수', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>69925205275</v>
+        <v>71451410250</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1079,14 +1079,14 @@
         <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>902000</v>
+        <v>1632000</v>
       </c>
       <c r="S7" t="n">
         <v>191000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>금리 인상 속에서도 60일선 돌파 및 추세 전환 기대감. 내일 FDC 수주 가능성 언급.</t>
+          <t>나스닥 반등과 함께 60일선 돌파 추세 전환 기대. 금리 인상에도 불구하고 한투의 집중 매수세 포착. 내일 FDC 수주 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['60일선', '추세 전환', 'FDC 수주']</t>
+          <t>['수주', '추세전환', '60일선']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10410</v>
+        <v>13470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.58</v>
+        <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>245</v>
+        <v>408</v>
       </c>
       <c r="H8" t="n">
-        <v>1.25</v>
+        <v>4.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9970</v>
+        <v>12920</v>
       </c>
       <c r="K8" t="n">
-        <v>10280</v>
+        <v>12920</v>
       </c>
       <c r="L8" t="n">
-        <v>11750</v>
+        <v>13770</v>
       </c>
       <c r="M8" t="n">
-        <v>10250</v>
+        <v>12910</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>5.12</v>
       </c>
       <c r="O8" t="n">
-        <v>173570070990</v>
+        <v>52806598520</v>
       </c>
       <c r="P8" t="n">
-        <v>15960</v>
+        <v>30200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3500</v>
+        <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>21000</v>
+        <v>-58000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감에도 불구하고, 주가 상승 동력이 외국인 및 기관 매도세로 인한 이탈 우려가 존재함.</t>
+          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['DCS계약', '원전', '추세']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13440</v>
+        <v>10480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+4.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.13</v>
+        <v>0.58</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>409</v>
+        <v>252</v>
       </c>
       <c r="H9" t="n">
-        <v>4.99</v>
+        <v>1.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12920</v>
+        <v>10070</v>
       </c>
       <c r="K9" t="n">
-        <v>12920</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13770</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>12910</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.12</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>52370785065</v>
+        <v>174140000000</v>
       </c>
       <c r="P9" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-110000</v>
+        <v>-18000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
+          <t>낙태약 및 탈모 치료 수혜주로 언급되며, 예상 매출 1조원 이상 기대. 그러나 주체로 추정되는 차명계좌에서의 매도 물량 출회 및 외국인 이탈 감지.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['DCS계약', '원전', '추세']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86500</v>
+        <v>86400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G10" t="n">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>97986812250</v>
+        <v>100755144300</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1355,14 +1355,14 @@
         <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-71000</v>
+        <v>-92000</v>
       </c>
       <c r="S10" t="n">
         <v>21000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 관련 사업 기대감 및 금리 인상 후 전망에 대한 긍정적인 언급이 있으나, 공매도 및 협상 불확실성 우려도 존재함.</t>
+          <t>FOMC 악재 종료 후 프로그램 매수세 전환. AP1000 관련 추정치 및 대미 원전 투자 재료 부각. 금리 인상 결정 속 원전 관련주 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전사업', '금리인상', '공매도']</t>
+          <t>['원전', '금리인상', '프로그램매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18680</v>
+        <v>18740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="H11" t="n">
         <v>10.85</v>
@@ -1438,7 +1438,7 @@
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>46765142140</v>
+        <v>47737679445</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,23 +1447,23 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-175000</v>
+        <v>-287000</v>
       </c>
       <c r="S11" t="n">
         <v>-76000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6천억원 규모 수주 발표에도 불구하고 주가 하락 및 금리 인상 우려. 대차해지 운동 동참 요청.</t>
+          <t>6천억 수주 발표에도 음봉 마감. 대차 해지 운동 독려하며 주가 부양 시도. 금리 인상 및 국장 투자에 대한 부정적 인식 언급. 알래스카 LNG 협의 결정 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '금리인상', '대차해지']</t>
+          <t>['수주', '대차해지', '금리인상']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254750</v>
+        <v>255250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>456</v>
       </c>
       <c r="G12" t="n">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1585568712000</v>
+        <v>1652228700500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1539,10 +1539,10 @@
         <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-199000</v>
+        <v>-678000</v>
       </c>
       <c r="S12" t="n">
-        <v>-231000</v>
+        <v>-191000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16130</v>
+        <v>16200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2.93</v>
       </c>
       <c r="E13" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F13" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G13" t="n">
-        <v>1287</v>
+        <v>1298</v>
       </c>
       <c r="H13" t="n">
         <v>4.88</v>
@@ -1622,7 +1622,7 @@
         <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>332899680850</v>
+        <v>334510381915</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1631,10 +1631,10 @@
         <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-508000</v>
+        <v>-749000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1759000</v>
+        <v>1763000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>1552</v>
+        <v>1570</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2857786595000</v>
+        <v>2963013915500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,7 +1723,7 @@
         <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-161000</v>
+        <v>-236000</v>
       </c>
       <c r="S14" t="n">
         <v>-62000</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>10896120035</v>
+        <v>11103040530</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1815,7 +1815,7 @@
         <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-263000</v>
+        <v>-335000</v>
       </c>
       <c r="S15" t="n">
         <v>-5000</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13750</v>
+        <v>13790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>14385820995</v>
+        <v>14581916195</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1907,7 +1907,7 @@
         <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>132000</v>
+        <v>122000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3460</v>
+        <v>10270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>298</v>
+        <v>118</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>18.42</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>10460</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>10860</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>11150</v>
       </c>
       <c r="M17" t="n">
-        <v>3420</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>19.22</v>
       </c>
       <c r="O17" t="n">
-        <v>5388929516</v>
+        <v>56295022395</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>-279000</v>
+        <v>-39000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '사기 주식']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10270</v>
+        <v>3450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-1.99%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="E18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F18" t="n">
         <v>51</v>
       </c>
-      <c r="F18" t="n">
-        <v>34</v>
-      </c>
       <c r="G18" t="n">
-        <v>116</v>
+        <v>304</v>
       </c>
       <c r="H18" t="n">
-        <v>18.42</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10460</v>
+        <v>3520</v>
       </c>
       <c r="K18" t="n">
-        <v>10860</v>
+        <v>3730</v>
       </c>
       <c r="L18" t="n">
-        <v>11150</v>
+        <v>3750</v>
       </c>
       <c r="M18" t="n">
-        <v>10060</v>
+        <v>3420</v>
       </c>
       <c r="N18" t="n">
-        <v>19.22</v>
+        <v>3.11</v>
       </c>
       <c r="O18" t="n">
-        <v>56082157465</v>
+        <v>5452426928</v>
       </c>
       <c r="P18" t="n">
-        <v>22450</v>
+        <v>16110</v>
       </c>
       <c r="Q18" t="n">
-        <v>1760</v>
+        <v>2300</v>
       </c>
       <c r="R18" t="n">
-        <v>-60000</v>
+        <v>-317000</v>
       </c>
       <c r="S18" t="n">
-        <v>-5000</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['상장폐지', '폭락', '사기 주식']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13190</v>
+        <v>13180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>81167332450</v>
+        <v>81331390620</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2183,7 +2183,7 @@
         <v>4600</v>
       </c>
       <c r="R19" t="n">
-        <v>-64000</v>
+        <v>-80000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4145</v>
+        <v>4175</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-5.33%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>48250819486</v>
+        <v>48560020597</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_13.xlsx
+++ b/data/trending_integrated_20260917_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>1716</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.21%</t>
+          <t>'+22.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="H2" t="n">
-        <v>3.71</v>
+        <v>3.52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>56</v>
+        <v>1397</v>
       </c>
       <c r="K2" t="n">
-        <v>56</v>
+        <v>1395</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>1800</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>1369</v>
       </c>
       <c r="N2" t="n">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>507669383</v>
+        <v>50768829052</v>
       </c>
       <c r="P2" t="n">
-        <v>901</v>
+        <v>5140</v>
       </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>870</v>
       </c>
       <c r="R2" t="n">
-        <v>30000</v>
+        <v>-32000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>코다코 부채 언급하며 비교. 개미 물량 이탈 시 100원대 회복 가능성 언급. 300원 이상 상승 기대 및 제2 대한광통신 가능성 제기. 지분 매수 공시 부재 및 거래량 부진.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['거래량', '개미', '공시']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1710</v>
+        <v>4535</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.41%</t>
+          <t>'+18.10%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>507</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="G3" t="n">
-        <v>117</v>
+        <v>1253</v>
       </c>
       <c r="H3" t="n">
-        <v>3.52</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1397</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>1395</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
-        <v>1369</v>
+        <v>3990</v>
       </c>
       <c r="N3" t="n">
-        <v>3.57</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>49816980709</v>
+        <v>242121247959</v>
       </c>
       <c r="P3" t="n">
-        <v>5140</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>870</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>-32000</v>
+        <v>-150000</v>
       </c>
       <c r="S3" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>카카오, 소프트뱅크 등 대규모 투자 및 인수설이 제기되며 텐배거 기대감 속에 급등세를 보임.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['인수', '텐배거', '소프트뱅크']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4570</v>
+        <v>21550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.01%</t>
+          <t>'+16.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>1231</v>
+        <v>256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>22950</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>239247765036</v>
+        <v>281850618420</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R4" t="n">
-        <v>-150000</v>
+        <v>-104000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대기업의 인수 및 투자 가능성에 대한 높은 기대감. 텐버거(10배 상승) 가능성 언급.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '소프트뱅크', '텐버거']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21850</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.73%</t>
+          <t>'+14.29%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>3.71</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18560</v>
+        <v>56</v>
       </c>
       <c r="K5" t="n">
-        <v>19260</v>
+        <v>56</v>
       </c>
       <c r="L5" t="n">
-        <v>22950</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
-        <v>18920</v>
+        <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92</v>
+        <v>3.71</v>
       </c>
       <c r="O5" t="n">
-        <v>279533239145</v>
+        <v>553393799</v>
       </c>
       <c r="P5" t="n">
-        <v>59600</v>
+        <v>901</v>
       </c>
       <c r="Q5" t="n">
-        <v>1030</v>
+        <v>56</v>
       </c>
       <c r="R5" t="n">
-        <v>-104000</v>
+        <v>30000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>코다코 부채 언급하며 비교. 개미 물량 이탈 시 100원대 회복 가능성 언급. 300원 이상 상승 기대 및 제2 대한광통신 가능성 제기. 지분 매수 공시 부재 및 거래량 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['거래량', '개미', '공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3870</v>
+        <v>3850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.57%</t>
+          <t>'+10.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>92493766784</v>
+        <v>93429842301</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
         <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>71451410250</v>
+        <v>72781069675</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등과 함께 60일선 돌파 추세 전환 기대. 금리 인상에도 불구하고 한투의 집중 매수세 포착. 내일 FDC 수주 공시 가능성 언급.</t>
+          <t>나스닥 반등과 함께 수주 기대감이 형성되고 있으나, 주가 변동성에 대한 의견이 엇갈림.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '추세전환', '60일선']</t>
+          <t>['수주', '추세 전환']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13470</v>
+        <v>10470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.26%</t>
+          <t>'+5.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.13</v>
+        <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>408</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
-        <v>4.99</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12920</v>
+        <v>9970</v>
       </c>
       <c r="K8" t="n">
-        <v>12920</v>
+        <v>10280</v>
       </c>
       <c r="L8" t="n">
-        <v>13770</v>
+        <v>11750</v>
       </c>
       <c r="M8" t="n">
-        <v>12910</v>
+        <v>10250</v>
       </c>
       <c r="N8" t="n">
-        <v>5.12</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>52806598520</v>
+        <v>174623693500</v>
       </c>
       <c r="P8" t="n">
-        <v>30200</v>
+        <v>15960</v>
       </c>
       <c r="Q8" t="n">
-        <v>3540</v>
+        <v>3500</v>
       </c>
       <c r="R8" t="n">
-        <v>-58000</v>
+        <v>-18000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
+          <t>낙태약 및 탈모 치료 수혜주로 언급되며, 예상 매출 1조원 이상 기대. 그러나 주체로 추정되는 차명계좌에서의 매도 물량 출회 및 외국인 이탈 감지.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['DCS계약', '원전', '추세']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10480</v>
+        <v>13490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.07%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.58</v>
+        <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>252</v>
+        <v>415</v>
       </c>
       <c r="H9" t="n">
-        <v>1.25</v>
+        <v>4.99</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10070</v>
+        <v>12920</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>12920</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>13770</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>12910</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>174140000000</v>
+        <v>55798502750</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-18000</v>
+        <v>-58000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 수혜주로 언급되며, 예상 매출 1조원 이상 기대. 그러나 주체로 추정되는 차명계좌에서의 매도 물량 출회 및 외국인 이탈 감지.</t>
+          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['DCS계약', '원전', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86400</v>
+        <v>86300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G10" t="n">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>100755144300</v>
+        <v>103666704350</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FOMC 악재 종료 후 프로그램 매수세 전환. AP1000 관련 추정치 및 대미 원전 투자 재료 부각. 금리 인상 결정 속 원전 관련주 동반 상승 기대.</t>
+          <t>FOMC 악재 소멸 후 원전 관련 투자 및 공매도 세력에 대한 기대감이 형성되며 주가 상승 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '금리인상', '프로그램매수']</t>
+          <t>['원전', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="G11" t="n">
-        <v>352</v>
+        <v>1320</v>
       </c>
       <c r="H11" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>18510</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>47737679445</v>
+        <v>336000530770</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-287000</v>
+        <v>-749000</v>
       </c>
       <c r="S11" t="n">
-        <v>-76000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6천억 수주 발표에도 음봉 마감. 대차 해지 운동 독려하며 주가 부양 시도. 금리 인상 및 국장 투자에 대한 부정적 인식 언급. 알래스카 LNG 협의 결정 기대.</t>
+          <t>미국 광통신 시장 호황 및 국내 통신 장비 부족 현상에 따른 수혜 기대감이 높으며, 매물대 소화 후 추가 상승 가능성이 분석됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '금리인상']</t>
+          <t>['광통신', '수혜주', '매물대소화']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>255250</v>
+        <v>18670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.69%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>456</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>1697</v>
+        <v>358</v>
       </c>
       <c r="H12" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K12" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L12" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M12" t="n">
-        <v>252000</v>
+        <v>18510</v>
       </c>
       <c r="N12" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1652228700500</v>
+        <v>48926307920</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-678000</v>
+        <v>-287000</v>
       </c>
       <c r="S12" t="n">
-        <v>-191000</v>
+        <v>-76000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 언급이 다수 포함되어 있으며, 주가 관련 구체적인 팩트 기반 분석은 부족함.</t>
+          <t>6천억 규모의 수주 발표에도 음봉 마감, 금리 인상 우려와 함께 대차해지 운동이 강조됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['수주', '대차해지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16200</v>
+        <v>254500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>247</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>135</v>
+        <v>450</v>
       </c>
       <c r="G13" t="n">
-        <v>1298</v>
+        <v>1671</v>
       </c>
       <c r="H13" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>16750</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>15560</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>334510381915</v>
+        <v>1735894024250</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-749000</v>
+        <v>-678000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-191000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호황 및 국내 통신 장비 부족 현상에 따른 수혜 기대감이 높으며, 매물대 소화 후 추가 상승 가능성이 분석됨.</t>
+          <t>정치적 이슈에 대한 논쟁이 주를 이루며, 일부 투자자들의 매도 움직임이 포착됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '수혜주', '매물대소화']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1763000</v>
+        <v>1761000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>1570</v>
+        <v>1588</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2963013915500</v>
+        <v>3057204425000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 단기적 반등 및 하락에 대한 기대가 혼재하며, 구체적인 팩트 기반 분석은 미흡함.</t>
+          <t>하반기 악재 소멸 기대감 속에서 개인 투자자들의 홀딩 및 매수 의견이 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주매입', '정치적악재']</t>
+          <t>['홀딩', '매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8430</v>
+        <v>8420</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>11103040530</v>
+        <v>11460168415</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13790</v>
+        <v>13760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
         <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>14581916195</v>
+        <v>14659843780</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 관련 변동성 언급, 외국인 대량 매수 및 매도 패턴 관찰. VI 예상 및 400~300원 띠기 가능성.</t>
+          <t>유가 변동성에 따른 주가 등락이 반복되며, 외국인 매수세에도 불구하고 하락세를 보임.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', 'VI']</t>
+          <t>['유가', '외국인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10270</v>
+        <v>3465</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>118</v>
+        <v>314</v>
       </c>
       <c r="H17" t="n">
-        <v>18.42</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10460</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>10860</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>11150</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>3420</v>
       </c>
       <c r="N17" t="n">
-        <v>19.22</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>56295022395</v>
+        <v>5525698813</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>-39000</v>
+        <v>-317000</v>
       </c>
       <c r="S17" t="n">
-        <v>-5000</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>급락세가 이어지며 상장폐지 가능성에 대한 우려가 제기되고, 주주들의 손실이 확대됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,112 +2015,112 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['상장폐지', '급락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3450</v>
+        <v>10230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.99%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>304</v>
+        <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>18.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3520</v>
+        <v>10460</v>
       </c>
       <c r="K18" t="n">
-        <v>3730</v>
+        <v>10860</v>
       </c>
       <c r="L18" t="n">
-        <v>3750</v>
+        <v>11150</v>
       </c>
       <c r="M18" t="n">
-        <v>3420</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>3.11</v>
+        <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>5452426928</v>
+        <v>56619031630</v>
       </c>
       <c r="P18" t="n">
-        <v>16110</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>2300</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>-317000</v>
+        <v>-39000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '사기 주식']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13180</v>
+        <v>13130</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>81331390620</v>
+        <v>81505705730</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4175</v>
+        <v>4165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.33%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>48560020597</v>
+        <v>49246292352</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_13.xlsx
+++ b/data/trending_integrated_20260917_13.xlsx
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1716</v>
+        <v>1706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.83%</t>
+          <t>'+22.12%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>128</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>50768829052</v>
+        <v>51158925229</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4535</v>
+        <v>21650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.10%</t>
+          <t>'+16.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>1253</v>
+        <v>260</v>
       </c>
       <c r="H3" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K3" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L3" t="n">
-        <v>4800</v>
+        <v>22950</v>
       </c>
       <c r="M3" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N3" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>242121247959</v>
+        <v>283033146145</v>
       </c>
       <c r="P3" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q3" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R3" t="n">
-        <v>-150000</v>
+        <v>-104000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대규모 투자 및 인수설이 제기되며 텐배거 기대감 속에 급등세를 보임.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수', '텐배거', '소프트뱅크']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21550</v>
+        <v>4440</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.11%</t>
+          <t>'+15.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>518</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="G4" t="n">
-        <v>256</v>
+        <v>1268</v>
       </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>0.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18560</v>
+        <v>3840</v>
       </c>
       <c r="K4" t="n">
-        <v>19260</v>
+        <v>4170</v>
       </c>
       <c r="L4" t="n">
-        <v>22950</v>
+        <v>4800</v>
       </c>
       <c r="M4" t="n">
-        <v>18920</v>
+        <v>3990</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>281850618420</v>
+        <v>246395224866</v>
       </c>
       <c r="P4" t="n">
-        <v>59600</v>
+        <v>6900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1030</v>
+        <v>1738</v>
       </c>
       <c r="R4" t="n">
-        <v>-104000</v>
+        <v>-150000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>카카오, 소프트뱅크 등 대규모 투자 및 인수설이 제기되며 텐배거 기대감 속에 급등세를 보임.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['인수', '텐배거', '소프트뱅크']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H5" t="n">
         <v>3.71</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3850</v>
+        <v>3825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.00%</t>
+          <t>'+9.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F6" t="n">
         <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>93429842301</v>
+        <v>94010150578</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 11%대 상승 시도. 프로그램 매수세 유입 확인. 스페이스X 관련주로 부각되며 5천원 돌파 기대감 언급. 일부 매물대 소화 및 매집봉 형태 관찰.</t>
+          <t>스페이스X 관련 사업 기대감과 함께 거래량 급증 및 주가 상승 추세가 나타났으나, 단기 차익 실현 및 프로그램 매도에 대한 언급도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '프로그램매수', '거래량']</t>
+          <t>['스페이스X', '거래량', '주가상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21700</v>
+        <v>21550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.43%</t>
+          <t>'+6.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
         <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>72781069675</v>
+        <v>74593220675</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등과 함께 수주 기대감이 형성되고 있으나, 주가 변동성에 대한 의견이 엇갈림.</t>
+          <t>나스닥 반등 및 FDC 수주 기대감 속에서 주가 상승 전망이 제기되었으나, 공매도 세력에 대한 언급과 주가 패턴 반복에 대한 지적 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '추세 전환']</t>
+          <t>['나스닥', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10470</v>
+        <v>10440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.02%</t>
+          <t>'+4.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>174623693500</v>
+        <v>174959807400</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 수혜주로 언급되며, 예상 매출 1조원 이상 기대. 그러나 주체로 추정되는 차명계좌에서의 매도 물량 출회 및 외국인 이탈 감지.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감에도 불구하고, 주포의 차익 실현 및 외국인 매도세 출현으로 인한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['낙태약', '탈모치료', '차익실현']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13490</v>
+        <v>13440</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>55798502750</v>
+        <v>56982460500</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86300</v>
+        <v>86500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F10" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>103666704350</v>
+        <v>106421313250</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16200</v>
+        <v>255500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.79%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>251</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>137</v>
+        <v>446</v>
       </c>
       <c r="G11" t="n">
-        <v>1320</v>
+        <v>1670</v>
       </c>
       <c r="H11" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K11" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L11" t="n">
-        <v>16750</v>
+        <v>259000</v>
       </c>
       <c r="M11" t="n">
-        <v>15560</v>
+        <v>252000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>336000530770</v>
+        <v>1810384516500</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R11" t="n">
-        <v>-749000</v>
+        <v>-678000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>-191000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호황 및 국내 통신 장비 부족 현상에 따른 수혜 기대감이 높으며, 매물대 소화 후 추가 상승 가능성이 분석됨.</t>
+          <t>정치적 이슈가 주식 관련 내용보다 더 많이 언급되었으며, 반도체 산업 전망 및 연기금 매매 동향에 대한 언급은 미미함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '수혜주', '매물대소화']</t>
+          <t>['반도체', '연기금', '정치']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18670</v>
+        <v>18700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
         <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="H12" t="n">
         <v>10.85</v>
@@ -1530,7 +1530,7 @@
         <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>48926307920</v>
+        <v>49816249090</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6천억 규모의 수주 발표에도 음봉 마감, 금리 인상 우려와 함께 대차해지 운동이 강조됨.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '대차해지']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254500</v>
+        <v>1767000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="G13" t="n">
-        <v>1671</v>
+        <v>1624</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>50.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>1759000</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>1770000</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>1785000</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>1735000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1735894024250</v>
+        <v>3167848951000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>-678000</v>
+        <v>-236000</v>
       </c>
       <c r="S13" t="n">
-        <v>-191000</v>
+        <v>-62000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 논쟁이 주를 이루며, 일부 투자자들의 매도 움직임이 포착됨.</t>
+          <t>하반기 악재 소멸 기대감 속에서 개인 투자자들의 홀딩 및 매수 의견이 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['홀딩', '매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1761000</v>
+        <v>16140</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>249</v>
       </c>
       <c r="F14" t="n">
-        <v>470</v>
+        <v>135</v>
       </c>
       <c r="G14" t="n">
-        <v>1588</v>
+        <v>1332</v>
       </c>
       <c r="H14" t="n">
-        <v>50.2</v>
+        <v>4.88</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1759000</v>
+        <v>16100</v>
       </c>
       <c r="K14" t="n">
-        <v>1770000</v>
+        <v>16200</v>
       </c>
       <c r="L14" t="n">
-        <v>1785000</v>
+        <v>16750</v>
       </c>
       <c r="M14" t="n">
-        <v>1735000</v>
+        <v>15560</v>
       </c>
       <c r="N14" t="n">
-        <v>50.2</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3057204425000</v>
+        <v>337680190175</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-236000</v>
+        <v>-749000</v>
       </c>
       <c r="S14" t="n">
-        <v>-62000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>하반기 악재 소멸 기대감 속에서 개인 투자자들의 홀딩 및 매수 의견이 나타남.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['홀딩', '매수']</t>
+          <t>['광통신', '수혜주', '매집']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8420</v>
+        <v>8440</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F15" t="n">
         <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>11460168415</v>
+        <v>11786202035</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>부정적인 전망과 함께 회사의 재무 건전성 및 경영 능력에 대한 비판이 제기되며, 주가 하락 가능성이 언급됨.</t>
+          <t>중국과의 경쟁 심화 및 회사 경영진 무능력에 대한 비판 속에서, 4분기 실적 개선 기대는 희미하며 주가 하락 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['재무건전성', '경영능력', '주가하락']</t>
+          <t>['디스플레이', '중국', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13760</v>
+        <v>3460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K16" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L16" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M16" t="n">
-        <v>13410</v>
+        <v>3420</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>14659843780</v>
+        <v>5567363458</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>122000</v>
+        <v>-317000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 주가 등락이 반복되며, 외국인 매수세에도 불구하고 하락세를 보임.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '외국인 매수']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3465</v>
+        <v>13730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M17" t="n">
-        <v>3420</v>
+        <v>13410</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5525698813</v>
+        <v>14858229370</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-317000</v>
+        <v>122000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급락세가 이어지며 상장폐지 가능성에 대한 우려가 제기되고, 주주들의 손실이 확대됨.</t>
+          <t>유가 변동성에 따른 단기적인 등락이 예상되며, 겨울 도래 및 지정학적 리스크가 주가에 영향을 미칠 가능성이 언급됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '급락']</t>
+          <t>['유가', '겨울', '지정학적']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H18" t="n">
         <v>18.42</v>
@@ -2082,7 +2082,7 @@
         <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>56619031630</v>
+        <v>56919117055</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13130</v>
+        <v>13150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.96%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" t="n">
         <v>1.76</v>
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>81505705730</v>
+        <v>81776797260</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2234,13 +2234,13 @@
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>49246292352</v>
+        <v>49647007273</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_13.xlsx
+++ b/data/trending_integrated_20260917_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.12%</t>
+          <t>'+22.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>51158925229</v>
+        <v>51620432005</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21650</v>
+        <v>4510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.65%</t>
+          <t>'+17.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>528</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>1271</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18560</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>19260</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>22950</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
-        <v>18920</v>
+        <v>3990</v>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>283033146145</v>
+        <v>249794510558</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>-104000</v>
+        <v>-150000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>카카오, 소프트뱅크 등 대기업 인수 관련 소문과 높은 기대감, 거래량 증가 및 10배 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['인수', '소프트뱅크', '카카오']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4440</v>
+        <v>21450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.62%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>518</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>1268</v>
+        <v>260</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>22950</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>246395224866</v>
+        <v>285203025120</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R4" t="n">
-        <v>-150000</v>
+        <v>-104000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대규모 투자 및 인수설이 제기되며 텐배거 기대감 속에 급등세를 보임.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '텐배거', '소프트뱅크']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3825</v>
+        <v>3845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.29%</t>
+          <t>'+9.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F6" t="n">
         <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>94010150578</v>
+        <v>94484645339</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 사업 기대감과 함께 거래량 급증 및 주가 상승 추세가 나타났으나, 단기 차익 실현 및 프로그램 매도에 대한 언급도 존재.</t>
+          <t>우주항공 관련 기대감과 함께 스페이스X 관련 언급, 주가 상승 및 매집 관련 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '거래량', '주가상승']</t>
+          <t>['우주항공', '스페이스X', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>74593220675</v>
+        <v>75977964875</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10440</v>
+        <v>10390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.71%</t>
+          <t>'+4.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>174959807400</v>
+        <v>175746930960</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13440</v>
+        <v>13450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>56982460500</v>
+        <v>57410387595</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>106421313250</v>
+        <v>108467805050</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FOMC 악재 소멸 후 원전 관련 투자 및 공매도 세력에 대한 기대감이 형성되며 주가 상승 전망이 제시됨.</t>
+          <t>미 금리 인상 및 대미 투자 관련 언급, 원전 관련 긍정적 전망과 프로그램 매수 전환에 대한 기대감이 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '공매도']</t>
+          <t>['금리 인상', '대미 투자', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G11" t="n">
-        <v>1670</v>
+        <v>1709</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>1810384516500</v>
+        <v>1884627266250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈가 주식 관련 내용보다 더 많이 언급되었으며, 반도체 산업 전망 및 연기금 매매 동향에 대한 언급은 미미함.</t>
+          <t>대통령 관련 정치적 언급이 주를 이루며, 주가 관련 내용은 미미함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '연기금', '정치']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18700</v>
+        <v>1769000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>478</v>
       </c>
       <c r="G12" t="n">
-        <v>316</v>
+        <v>1641</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>1759000</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>1770000</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>1785000</v>
       </c>
       <c r="M12" t="n">
-        <v>18510</v>
+        <v>1735000</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>49816249090</v>
+        <v>3323974073500</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>-287000</v>
+        <v>-236000</v>
       </c>
       <c r="S12" t="n">
-        <v>-76000</v>
+        <v>-62000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>자사주 매입 및 실적 시즌 언급, 가격 상승 기대감이 존재하나 구체적 근거는 부족함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['실적 시즌', '자사주 매입']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1767000</v>
+        <v>16170</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>253</v>
       </c>
       <c r="F13" t="n">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="G13" t="n">
-        <v>1624</v>
+        <v>1353</v>
       </c>
       <c r="H13" t="n">
-        <v>50.2</v>
+        <v>4.88</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1759000</v>
+        <v>16100</v>
       </c>
       <c r="K13" t="n">
-        <v>1770000</v>
+        <v>16200</v>
       </c>
       <c r="L13" t="n">
-        <v>1785000</v>
+        <v>16750</v>
       </c>
       <c r="M13" t="n">
-        <v>1735000</v>
+        <v>15560</v>
       </c>
       <c r="N13" t="n">
-        <v>50.2</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3167848951000</v>
+        <v>338955529425</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-236000</v>
+        <v>-749000</v>
       </c>
       <c r="S13" t="n">
-        <v>-62000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>하반기 악재 소멸 기대감 속에서 개인 투자자들의 홀딩 및 매수 의견이 나타남.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['홀딩', '매수']</t>
+          <t>['광통신', '수혜주', '매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16140</v>
+        <v>18650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>249</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>1332</v>
+        <v>324</v>
       </c>
       <c r="H14" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K14" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L14" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M14" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O14" t="n">
-        <v>337680190175</v>
+        <v>50380746830</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-749000</v>
+        <v>-287000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-76000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '수혜주', '매집']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>11786202035</v>
+        <v>12025299165</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>중국과의 경쟁 심화 및 회사 경영진 무능력에 대한 비판 속에서, 4분기 실적 개선 기대는 희미하며 주가 하락 우려가 제기됨.</t>
+          <t>4분기 전망 및 영업이익 언급이 있으나, 중국 경쟁력 약화, 높은 부채 등 부정적 요인이 다수 제기됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['디스플레이', '중국', '경영진']</t>
+          <t>['영업이익', '부채']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3460</v>
+        <v>3465</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1898,7 +1898,7 @@
         <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>5567363458</v>
+        <v>5604481068</v>
       </c>
       <c r="P16" t="n">
         <v>16110</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13730</v>
+        <v>13690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H17" t="n">
         <v>0.01</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>14858229370</v>
+        <v>15177876590</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 단기적인 등락이 예상되며, 겨울 도래 및 지정학적 리스크가 주가에 영향을 미칠 가능성이 언급됨.</t>
+          <t>유가 변동 및 겨울 도래에 따른 가격 상승 기대감, 외국인 매수세 언급되나 불확실성도 공존.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '겨울', '지정학적']</t>
+          <t>['유가', '외국인 매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,7 +2050,7 @@
         <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
@@ -2082,7 +2082,7 @@
         <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>56919117055</v>
+        <v>57041764545</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13150</v>
+        <v>13230</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
         <v>36</v>
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>81776797260</v>
+        <v>81950793565</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4165</v>
+        <v>4145</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.56%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>49647007273</v>
+        <v>49956222213</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
